--- a/Design-Files/Termination-Board-v1.0.1/Deliverables/BOM/Client_BOM_Termination-Board-V1.0.1.xlsx
+++ b/Design-Files/Termination-Board-v1.0.1/Deliverables/BOM/Client_BOM_Termination-Board-V1.0.1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\benjamin-rcctledboard-hw\Design-Files\Termination-Board-v1.0.0\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\benjamin-rcctledboard-hw\Design-Files\Termination-Board-v1.0.1\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -75,19 +75,19 @@
     <t>CAP CER 1UF 100V X7S 0805</t>
   </si>
   <si>
-    <t>DIODE SCHOTTKY 60V 2A SMA</t>
+    <t>SCHOTTKY DIODE SMB 100V 5A</t>
   </si>
   <si>
     <t>SMB(DO-214AA) TVS ROHS</t>
   </si>
   <si>
-    <t>33V 1.1A 40A 2.2A 1812 Resettable Fuses ROHS</t>
-  </si>
-  <si>
-    <t>CONN HEADER SMD R/A 5POS 2MM</t>
-  </si>
-  <si>
-    <t>CONN PWR JACK 2X5.5MM SOLDER</t>
+    <t>30V 3.3A 40A 6.6A 2920 Resettable Fuses ROHS</t>
+  </si>
+  <si>
+    <t>CONN HEADER R/A 5POS 2.5MM</t>
+  </si>
+  <si>
+    <t>Bend insert DC Power Receptacle -20℃~+70℃ 1.3mm 5mm 3.5A 24V Plugin DC Power Connectors ROHS</t>
   </si>
   <si>
     <t>Footprint</t>
@@ -102,13 +102,16 @@
     <t>Cap-0805</t>
   </si>
   <si>
-    <t>SMA</t>
-  </si>
-  <si>
-    <t>S5B-PH-SM4-TB(LF)(SN)</t>
-  </si>
-  <si>
-    <t>PJ-051AH</t>
+    <t>SMB Bi Directional</t>
+  </si>
+  <si>
+    <t>Fuse-2920</t>
+  </si>
+  <si>
+    <t>S5B-XH-A(LF)(SN)</t>
+  </si>
+  <si>
+    <t>DC-003A-3.5A-1.3</t>
   </si>
   <si>
     <t>Manufacturer Part Number</t>
@@ -120,13 +123,13 @@
     <t>GCM21BC72A105KE36L</t>
   </si>
   <si>
-    <t>B260A-13-F</t>
+    <t>SS510B</t>
   </si>
   <si>
     <t>SMBJ26CA</t>
   </si>
   <si>
-    <t>BSMD1812-150-33V</t>
+    <t>BSMD2920-330-30V</t>
   </si>
   <si>
     <t>Manufacturer</t>
@@ -141,7 +144,7 @@
     <t>Murata</t>
   </si>
   <si>
-    <t>Diodes</t>
+    <t>MDD</t>
   </si>
   <si>
     <t>MSKSEMI</t>
@@ -153,7 +156,7 @@
     <t>JST</t>
   </si>
   <si>
-    <t>CUI Devices</t>
+    <t>XKB Connection</t>
   </si>
   <si>
     <t>47uF</t>
@@ -177,16 +180,13 @@
     <t>Connector</t>
   </si>
   <si>
-    <t>Fuse-1812</t>
+    <t>-</t>
+  </si>
+  <si>
+    <t>SMB</t>
   </si>
   <si>
     <t>Custom</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>SMB (DO-214AA)</t>
   </si>
 </sst>
 </file>
@@ -725,19 +725,19 @@
         <v>23</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I2" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="K2" s="5" t="s">
         <v>50</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -756,16 +756,16 @@
         <v>15</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>24</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J3" s="7">
         <v>2</v>
@@ -778,7 +778,7 @@
         <f t="shared" ref="B4:B10" si="0">ROW(B4) - ROW($B$2)</f>
         <v>2</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="12" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="9" t="s">
@@ -791,13 +791,13 @@
         <v>25</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J4" s="9">
         <v>1</v>
@@ -810,7 +810,7 @@
         <f>ROW(B5) - ROW($B$2)</f>
         <v>3</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="13" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="7" t="s">
@@ -823,13 +823,13 @@
         <v>26</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J5" s="7">
         <v>1</v>
@@ -852,16 +852,16 @@
         <v>18</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J6" s="9">
         <v>1</v>
@@ -884,16 +884,16 @@
         <v>19</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J7" s="7">
         <v>1</v>
@@ -916,16 +916,16 @@
         <v>20</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J8" s="9">
         <v>1</v>
@@ -938,8 +938,8 @@
         <f>ROW(B9) - ROW($B$2)</f>
         <v>7</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>51</v>
+      <c r="C9" s="13" t="s">
+        <v>52</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>12</v>
@@ -948,30 +948,30 @@
         <v>21</v>
       </c>
       <c r="F9" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" s="8" t="s">
         <v>53</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>54</v>
       </c>
       <c r="J9" s="7">
         <v>1</v>
       </c>
       <c r="K9" s="7"/>
     </row>
-    <row r="10" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="11">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>13</v>
@@ -979,17 +979,17 @@
       <c r="E10" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>54</v>
       </c>
       <c r="J10" s="9">
         <v>1</v>

--- a/Design-Files/Termination-Board-v1.0.1/Deliverables/BOM/Client_BOM_Termination-Board-V1.0.1.xlsx
+++ b/Design-Files/Termination-Board-v1.0.1/Deliverables/BOM/Client_BOM_Termination-Board-V1.0.1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\benjamin-rcctledboard-hw\Design-Files\Termination-Board-v1.0.1\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-consultants\benjamin-rcctledboard-hw\Design-Files\Termination-Board-v1.0.1\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -69,9 +69,6 @@
     <t>47uF 50V 66mA@120Hz ±20% SMD,D6.3xL7.7mm Aluminum Electrolytic Capacitors - SMD ROHS</t>
   </si>
   <si>
-    <t>CAP CER 0.1UF 25V X7R 0603</t>
-  </si>
-  <si>
     <t>CAP CER 1UF 100V X7S 0805</t>
   </si>
   <si>
@@ -117,9 +114,6 @@
     <t>Manufacturer Part Number</t>
   </si>
   <si>
-    <t>CC0603JRX7R8BB104</t>
-  </si>
-  <si>
     <t>GCM21BC72A105KE36L</t>
   </si>
   <si>
@@ -187,6 +181,12 @@
   </si>
   <si>
     <t>Custom</t>
+  </si>
+  <si>
+    <t>CC0603JRX7R9BB104</t>
+  </si>
+  <si>
+    <t>CAP CER 0.1UF 50V X7R 0603</t>
   </si>
 </sst>
 </file>
@@ -680,21 +680,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="3.140625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.109375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="29.42578125" customWidth="1"/>
+    <col min="6" max="6" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="29.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -707,7 +707,7 @@
       <c r="J1" s="14"/>
       <c r="K1" s="14"/>
     </row>
-    <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="5" t="s">
         <v>0</v>
@@ -722,25 +722,25 @@
         <v>14</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="11">
         <f>ROW(B3) - ROW($B$2)</f>
@@ -756,23 +756,23 @@
         <v>15</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J3" s="7">
         <v>2</v>
       </c>
       <c r="K3" s="7"/>
     </row>
-    <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="11">
         <f t="shared" ref="B4:B10" si="0">ROW(B4) - ROW($B$2)</f>
@@ -785,26 +785,26 @@
         <v>7</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J4" s="9">
         <v>1</v>
       </c>
       <c r="K4" s="9"/>
     </row>
-    <row r="5" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="11">
         <f>ROW(B5) - ROW($B$2)</f>
@@ -817,26 +817,26 @@
         <v>8</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J5" s="7">
         <v>1</v>
       </c>
       <c r="K5" s="7"/>
     </row>
-    <row r="6" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="11">
         <f t="shared" si="0"/>
@@ -849,26 +849,26 @@
         <v>9</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J6" s="9">
         <v>1</v>
       </c>
       <c r="K6" s="9"/>
     </row>
-    <row r="7" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1"/>
       <c r="B7" s="11">
         <f>ROW(B7) - ROW($B$2)</f>
@@ -881,26 +881,26 @@
         <v>10</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J7" s="7">
         <v>1</v>
       </c>
       <c r="K7" s="7"/>
     </row>
-    <row r="8" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
       <c r="B8" s="11">
         <f t="shared" si="0"/>
@@ -913,83 +913,83 @@
         <v>11</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J8" s="9">
         <v>1</v>
       </c>
       <c r="K8" s="9"/>
     </row>
-    <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
       <c r="B9" s="11">
         <f>ROW(B9) - ROW($B$2)</f>
         <v>7</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J9" s="7">
         <v>1</v>
       </c>
       <c r="K9" s="7"/>
     </row>
-    <row r="10" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1"/>
       <c r="B10" s="11">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>13</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J10" s="9">
         <v>1</v>

--- a/Design-Files/Termination-Board-v1.0.1/Deliverables/BOM/Client_BOM_Termination-Board-V1.0.1.xlsx
+++ b/Design-Files/Termination-Board-v1.0.1/Deliverables/BOM/Client_BOM_Termination-Board-V1.0.1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-consultants\benjamin-rcctledboard-hw\Design-Files\Termination-Board-v1.0.1\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\benjamin-rcctledboard-hw\Design-Files\Termination-Board-v1.0.1\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -69,6 +69,9 @@
     <t>47uF 50V 66mA@120Hz ±20% SMD,D6.3xL7.7mm Aluminum Electrolytic Capacitors - SMD ROHS</t>
   </si>
   <si>
+    <t>CAP CER 0.1UF 50V X7R 0603</t>
+  </si>
+  <si>
     <t>CAP CER 1UF 100V X7S 0805</t>
   </si>
   <si>
@@ -84,7 +87,7 @@
     <t>CONN HEADER R/A 5POS 2.5MM</t>
   </si>
   <si>
-    <t>Bend insert DC Power Receptacle -20℃~+70℃ 1.3mm 5mm 3.5A 24V Plugin DC Power Connectors ROHS</t>
+    <t>Bend insert DC Power Receptacle -30℃~+85℃ 2.5mm 6mm 7A 24V Plugin DC Power Connectors ROHS</t>
   </si>
   <si>
     <t>Footprint</t>
@@ -108,12 +111,15 @@
     <t>S5B-XH-A(LF)(SN)</t>
   </si>
   <si>
-    <t>DC-003A-3.5A-1.3</t>
+    <t>DC-044K-D025</t>
   </si>
   <si>
     <t>Manufacturer Part Number</t>
   </si>
   <si>
+    <t>CC0603JRX7R9BB104</t>
+  </si>
+  <si>
     <t>GCM21BC72A105KE36L</t>
   </si>
   <si>
@@ -150,7 +156,7 @@
     <t>JST</t>
   </si>
   <si>
-    <t>XKB Connection</t>
+    <t>G-Switch</t>
   </si>
   <si>
     <t>47uF</t>
@@ -177,16 +183,10 @@
     <t>-</t>
   </si>
   <si>
+    <t>Custom</t>
+  </si>
+  <si>
     <t>SMB</t>
-  </si>
-  <si>
-    <t>Custom</t>
-  </si>
-  <si>
-    <t>CC0603JRX7R9BB104</t>
-  </si>
-  <si>
-    <t>CAP CER 0.1UF 50V X7R 0603</t>
   </si>
 </sst>
 </file>
@@ -680,21 +680,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="3.109375" style="4" customWidth="1"/>
-    <col min="3" max="3" width="18.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.140625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="29.44140625" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="29.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -707,7 +707,7 @@
       <c r="J1" s="14"/>
       <c r="K1" s="14"/>
     </row>
-    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="5" t="s">
         <v>0</v>
@@ -722,25 +722,25 @@
         <v>14</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I2" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>47</v>
-      </c>
       <c r="K2" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="11">
         <f>ROW(B3) - ROW($B$2)</f>
@@ -756,55 +756,55 @@
         <v>15</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J3" s="7">
         <v>2</v>
       </c>
       <c r="K3" s="7"/>
     </row>
-    <row r="4" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="11">
         <f t="shared" ref="B4:B10" si="0">ROW(B4) - ROW($B$2)</f>
         <v>2</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="13" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J4" s="9">
         <v>1</v>
       </c>
       <c r="K4" s="9"/>
     </row>
-    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="11">
         <f>ROW(B5) - ROW($B$2)</f>
@@ -817,26 +817,26 @@
         <v>8</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J5" s="7">
         <v>1</v>
       </c>
       <c r="K5" s="7"/>
     </row>
-    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="11">
         <f t="shared" si="0"/>
@@ -849,26 +849,26 @@
         <v>9</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J6" s="9">
         <v>1</v>
       </c>
       <c r="K6" s="9"/>
     </row>
-    <row r="7" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="11">
         <f>ROW(B7) - ROW($B$2)</f>
@@ -881,26 +881,26 @@
         <v>10</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J7" s="7">
         <v>1</v>
       </c>
       <c r="K7" s="7"/>
     </row>
-    <row r="8" spans="1:11" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="11">
         <f t="shared" si="0"/>
@@ -913,83 +913,83 @@
         <v>11</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J8" s="9">
         <v>1</v>
       </c>
       <c r="K8" s="9"/>
     </row>
-    <row r="9" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="11">
         <f>ROW(B9) - ROW($B$2)</f>
         <v>7</v>
       </c>
-      <c r="C9" s="13" t="s">
-        <v>50</v>
+      <c r="C9" s="12" t="s">
+        <v>52</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F9" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" s="8" t="s">
         <v>53</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>51</v>
       </c>
       <c r="J9" s="7">
         <v>1</v>
       </c>
       <c r="K9" s="7"/>
     </row>
-    <row r="10" spans="1:11" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="11">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>13</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F10" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>51</v>
       </c>
       <c r="J10" s="9">
         <v>1</v>
